--- a/‎⁨تدقيق حسابات الجوهره⁩.xlsx
+++ b/‎⁨تدقيق حسابات الجوهره⁩.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JAWHER PC 1\OneDrive\Desktop\JWHERA CO\نضا\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E42B34B-0EC7-4979-995C-D0D0EEC0DE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D74CDF0-8DEF-490C-9A57-7B4036B3973D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CF1ADEA-A8E3-4C0D-9BF1-5D907AC6645E}"/>
   </bookViews>
@@ -201,7 +201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3035" uniqueCount="1527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3047" uniqueCount="1535">
   <si>
     <t>ت</t>
   </si>
@@ -4782,6 +4782,30 @@
   </si>
   <si>
     <t>Column1</t>
+  </si>
+  <si>
+    <t>1914</t>
+  </si>
+  <si>
+    <t>ايراد دفعة كهرباء</t>
+  </si>
+  <si>
+    <t>محمد خلف سلطان</t>
+  </si>
+  <si>
+    <t>تسديد مبلغ- دفعه كهرباء</t>
+  </si>
+  <si>
+    <t>1916</t>
+  </si>
+  <si>
+    <t>ارجاع مبلغ – الوصل 1896 الى محمد عباس</t>
+  </si>
+  <si>
+    <t>1915</t>
+  </si>
+  <si>
+    <t>قبض مبلغ - صرف في وصل 1896</t>
   </si>
 </sst>
 </file>
@@ -5055,7 +5079,7 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5188,6 +5212,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="20% - Accent3" xfId="1" builtinId="38"/>
@@ -5197,7 +5222,28 @@
     <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="37">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -5370,6 +5416,16 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5677,17 +5733,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I883" totalsRowShown="0" headerRowDxfId="33" headerRowBorderDxfId="32" headerRowCellStyle="20% - Accent3">
-  <autoFilter ref="A1:I883" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}" name="Table2" displayName="Table2" ref="A1:I884" totalsRowShown="0" headerRowDxfId="36" headerRowBorderDxfId="35" headerRowCellStyle="20% - Accent3">
+  <autoFilter ref="A1:I884" xr:uid="{B2B58B3A-509A-4784-BEF8-B8E0E5B7893E}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{99E4BA92-7CF2-47F7-BB5E-C225056D0686}" name="ت" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{099DC4E0-0CFC-4492-ADF4-6C60B3444A44}" name="الوصل" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{1FA9FD82-2BE3-449F-BF3F-BC1D9B438AF8}" name="التاريخ" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{F6462CAD-00B7-4743-905E-30546332391E}" name="النوع" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{4AFE8035-B5F3-4BD1-8F0A-ABA4412EF353}" name="الاسم" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{27F7889C-AB1D-4AD8-AA45-066551172103}" name="التفاصيل" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{89CD4CA4-724D-4A19-960F-E3C1BA0D25AE}" name="مبلغ الصرفيات" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{947E2160-EB43-4D87-BB0B-B0C789A460EA}" name="مبلغ إيرادات" dataDxfId="27"/>
     <tableColumn id="9" xr3:uid="{81AA4F3D-B22F-40E0-9E7D-2A89E3D37059}" name="Column1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -5991,7 +6047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BEB6ED-94C7-41EE-9181-BEC3BCA0AE6B}">
-  <dimension ref="A1:I883"/>
+  <dimension ref="A1:I884"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -23793,34 +23849,34 @@
         <v>743</v>
       </c>
       <c r="B744" s="4" t="s">
-        <v>1495</v>
+        <v>1533</v>
       </c>
       <c r="C744" s="5">
         <v>46260</v>
       </c>
       <c r="D744" s="6" t="s">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="E744" s="7" t="s">
-        <v>1496</v>
+        <v>147</v>
       </c>
       <c r="F744" s="7" t="s">
-        <v>1497</v>
-      </c>
-      <c r="G744" s="8">
+        <v>1534</v>
+      </c>
+      <c r="G744" s="7"/>
+      <c r="H744" s="8">
         <v>20000000</v>
       </c>
-      <c r="H744" s="9"/>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A745" s="15">
         <v>744</v>
       </c>
       <c r="B745" s="4" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="C745" s="5">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="D745" s="6" t="s">
         <v>92</v>
@@ -23829,10 +23885,10 @@
         <v>1496</v>
       </c>
       <c r="F745" s="7" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="G745" s="8">
-        <v>5000000</v>
+        <v>20000000</v>
       </c>
       <c r="H745" s="9"/>
     </row>
@@ -23841,22 +23897,22 @@
         <v>745</v>
       </c>
       <c r="B746" s="4" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="C746" s="5">
         <v>46261</v>
       </c>
       <c r="D746" s="6" t="s">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="E746" s="7" t="s">
-        <v>83</v>
+        <v>1496</v>
       </c>
       <c r="F746" s="7" t="s">
-        <v>1075</v>
+        <v>1499</v>
       </c>
       <c r="G746" s="8">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="H746" s="9"/>
     </row>
@@ -23865,22 +23921,22 @@
         <v>746</v>
       </c>
       <c r="B747" s="4" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="C747" s="5">
-        <v>46263</v>
+        <v>46261</v>
       </c>
       <c r="D747" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E747" s="7" t="s">
-        <v>1502</v>
+        <v>83</v>
       </c>
       <c r="F747" s="7" t="s">
-        <v>1503</v>
+        <v>1075</v>
       </c>
       <c r="G747" s="8">
-        <v>810000</v>
+        <v>500000</v>
       </c>
       <c r="H747" s="9"/>
     </row>
@@ -23889,79 +23945,79 @@
         <v>747</v>
       </c>
       <c r="B748" s="4" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="C748" s="5">
         <v>46263</v>
       </c>
       <c r="D748" s="6" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="E748" s="7" t="s">
-        <v>116</v>
+        <v>1502</v>
       </c>
       <c r="F748" s="7" t="s">
-        <v>1505</v>
-      </c>
-      <c r="G748" s="7"/>
-      <c r="H748" s="45">
-        <v>10000000</v>
-      </c>
+        <v>1503</v>
+      </c>
+      <c r="G748" s="8">
+        <v>810000</v>
+      </c>
+      <c r="H748" s="9"/>
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A749" s="15">
         <v>748</v>
       </c>
       <c r="B749" s="4" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="C749" s="5">
         <v>46263</v>
       </c>
       <c r="D749" s="6" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="E749" s="7" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
       <c r="F749" s="7" t="s">
-        <v>1507</v>
-      </c>
-      <c r="G749" s="8">
-        <v>35000</v>
-      </c>
-      <c r="H749" s="9"/>
-    </row>
-    <row r="750" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1505</v>
+      </c>
+      <c r="G749" s="7"/>
+      <c r="H749" s="45">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="750" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A750" s="15">
         <v>749</v>
       </c>
       <c r="B750" s="4" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="C750" s="5">
         <v>46263</v>
       </c>
       <c r="D750" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E750" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="F750" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="G750" s="7"/>
-      <c r="H750" s="45">
-        <v>10000000</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="F750" s="7" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G750" s="8">
+        <v>35000</v>
+      </c>
+      <c r="H750" s="9"/>
     </row>
     <row r="751" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A751" s="15">
         <v>750</v>
       </c>
       <c r="B751" s="4" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="C751" s="5">
         <v>46263</v>
@@ -23970,46 +24026,46 @@
         <v>15</v>
       </c>
       <c r="E751" s="7" t="s">
-        <v>866</v>
+        <v>298</v>
       </c>
       <c r="F751" s="11" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G751" s="7"/>
       <c r="H751" s="45">
         <v>10000000</v>
       </c>
     </row>
-    <row r="752" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A752" s="15">
         <v>751</v>
       </c>
       <c r="B752" s="4" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="C752" s="5">
         <v>46263</v>
       </c>
       <c r="D752" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E752" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="F752" s="7" t="s">
-        <v>1511</v>
-      </c>
-      <c r="G752" s="8">
-        <v>1000000</v>
-      </c>
-      <c r="H752" s="9"/>
+        <v>866</v>
+      </c>
+      <c r="F752" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="G752" s="7"/>
+      <c r="H752" s="45">
+        <v>10000000</v>
+      </c>
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A753" s="15">
         <v>752</v>
       </c>
       <c r="B753" s="4" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="C753" s="5">
         <v>46263</v>
@@ -24021,7 +24077,7 @@
         <v>151</v>
       </c>
       <c r="F753" s="7" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="G753" s="8">
         <v>1000000</v>
@@ -24033,7 +24089,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="4" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="C754" s="5">
         <v>46263</v>
@@ -24042,70 +24098,70 @@
         <v>7</v>
       </c>
       <c r="E754" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="F754" s="39" t="s">
-        <v>1515</v>
+        <v>151</v>
+      </c>
+      <c r="F754" s="7" t="s">
+        <v>1513</v>
       </c>
       <c r="G754" s="8">
-        <v>1150000</v>
+        <v>1000000</v>
       </c>
       <c r="H754" s="9"/>
     </row>
-    <row r="755" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A755" s="15">
         <v>754</v>
       </c>
       <c r="B755" s="4" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="C755" s="5">
         <v>46263</v>
       </c>
       <c r="D755" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E755" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="F755" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="G755" s="7"/>
-      <c r="H755" s="45">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="756" spans="1:8" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="F755" s="39" t="s">
+        <v>1515</v>
+      </c>
+      <c r="G755" s="8">
+        <v>1150000</v>
+      </c>
+      <c r="H755" s="9"/>
+    </row>
+    <row r="756" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A756" s="15">
         <v>755</v>
       </c>
       <c r="B756" s="4" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C756" s="5">
         <v>46263</v>
       </c>
       <c r="D756" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E756" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="F756" s="7" t="s">
-        <v>1518</v>
-      </c>
-      <c r="G756" s="8">
-        <v>1100000</v>
-      </c>
-      <c r="H756" s="9"/>
+        <v>203</v>
+      </c>
+      <c r="F756" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="G756" s="7"/>
+      <c r="H756" s="45">
+        <v>3000000</v>
+      </c>
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A757" s="15">
         <v>756</v>
       </c>
       <c r="B757" s="4" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="C757" s="5">
         <v>46263</v>
@@ -24117,10 +24173,10 @@
         <v>241</v>
       </c>
       <c r="F757" s="7" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="G757" s="8">
-        <v>25000</v>
+        <v>1100000</v>
       </c>
       <c r="H757" s="9"/>
     </row>
@@ -24129,7 +24185,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="4" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="C758" s="5">
         <v>46263</v>
@@ -24138,13 +24194,13 @@
         <v>7</v>
       </c>
       <c r="E758" s="7" t="s">
-        <v>1522</v>
+        <v>241</v>
       </c>
       <c r="F758" s="7" t="s">
-        <v>278</v>
+        <v>1520</v>
       </c>
       <c r="G758" s="8">
-        <v>1940000</v>
+        <v>25000</v>
       </c>
       <c r="H758" s="9"/>
     </row>
@@ -24153,7 +24209,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="4" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="C759" s="5">
         <v>46263</v>
@@ -24162,13 +24218,13 @@
         <v>7</v>
       </c>
       <c r="E759" s="7" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="F759" s="7" t="s">
-        <v>1525</v>
+        <v>278</v>
       </c>
       <c r="G759" s="8">
-        <v>4907000</v>
+        <v>1940000</v>
       </c>
       <c r="H759" s="9"/>
     </row>
@@ -24176,36 +24232,72 @@
       <c r="A760" s="15">
         <v>759</v>
       </c>
-      <c r="B760" s="4"/>
-      <c r="C760" s="5"/>
-      <c r="D760" s="6"/>
-      <c r="E760" s="7"/>
-      <c r="F760" s="7"/>
-      <c r="G760" s="8"/>
+      <c r="B760" s="4" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C760" s="5">
+        <v>46263</v>
+      </c>
+      <c r="D760" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E760" s="7" t="s">
+        <v>1524</v>
+      </c>
+      <c r="F760" s="7" t="s">
+        <v>1525</v>
+      </c>
+      <c r="G760" s="8">
+        <v>4907000</v>
+      </c>
       <c r="H760" s="9"/>
     </row>
     <row r="761" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A761" s="15">
         <v>760</v>
       </c>
-      <c r="B761" s="4"/>
-      <c r="C761" s="5"/>
-      <c r="D761" s="6"/>
-      <c r="E761" s="7"/>
-      <c r="F761" s="7"/>
-      <c r="G761" s="8"/>
-      <c r="H761" s="9"/>
+      <c r="B761" s="4" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C761" s="5">
+        <v>46264</v>
+      </c>
+      <c r="D761" s="6" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E761" s="7" t="s">
+        <v>1529</v>
+      </c>
+      <c r="F761" s="7" t="s">
+        <v>1530</v>
+      </c>
+      <c r="G761" s="7"/>
+      <c r="H761" s="46">
+        <v>7500000</v>
+      </c>
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A762" s="15">
         <v>761</v>
       </c>
-      <c r="B762" s="4"/>
-      <c r="C762" s="5"/>
-      <c r="D762" s="6"/>
-      <c r="E762" s="7"/>
-      <c r="F762" s="7"/>
-      <c r="G762" s="8"/>
+      <c r="B762" s="4" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C762" s="5">
+        <v>46264</v>
+      </c>
+      <c r="D762" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E762" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F762" s="39" t="s">
+        <v>1532</v>
+      </c>
+      <c r="G762" s="8">
+        <v>20000000</v>
+      </c>
       <c r="H762" s="9"/>
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.25">
@@ -25660,107 +25752,130 @@
       <c r="G883" s="8"/>
       <c r="H883" s="9"/>
     </row>
+    <row r="884" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A884" s="15">
+        <v>883</v>
+      </c>
+      <c r="B884" s="4"/>
+      <c r="C884" s="5"/>
+      <c r="D884" s="6"/>
+      <c r="E884" s="7"/>
+      <c r="F884" s="7"/>
+      <c r="G884" s="8"/>
+      <c r="H884" s="9"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B664">
-    <cfRule type="duplicateValues" dxfId="23" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B665:B676">
-    <cfRule type="duplicateValues" dxfId="22" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B677:B690">
-    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691:B705">
-    <cfRule type="duplicateValues" dxfId="20" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B719">
-    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B720:B726">
-    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B727:B731">
-    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B732:B744">
-    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
+  <conditionalFormatting sqref="B732:B743 B745">
+    <cfRule type="duplicateValues" dxfId="19" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9 G13:G14 G16:G22">
-    <cfRule type="expression" dxfId="15" priority="46" stopIfTrue="1">
-      <formula>P3:P2006&gt;110000000</formula>
+  <conditionalFormatting sqref="B746:B760">
+    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G111:G115 G118:G143 G145:G155 G160:G162 G165 G167:G174 G177:G180 G183:G196 G199:G202 G204:G208 G210:G214 G216:G218 G220 G225:G233 G237:G239 G243:G246 G248:G249 G254:G258 G260:G261 G263:G268 G271 G273:G282 G286 G290:G299 G302:G306 G308 G310:G316 G318:G323 G325:G333 G336:G351 G353:G356 G359:G363 G365:G378">
+    <cfRule type="expression" dxfId="17" priority="50" stopIfTrue="1">
+      <formula>P112:P2115&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G27:G34">
-    <cfRule type="expression" dxfId="14" priority="42" stopIfTrue="1">
-      <formula>P28:P2031&gt;110000000</formula>
+  <conditionalFormatting sqref="G88 G35:G50 G53:G54 G57:G63 G65:G70 G72:G79 G81:G86 G90 G95:G101 G106 G108 G380:G383">
+    <cfRule type="expression" dxfId="16" priority="58" stopIfTrue="1">
+      <formula>P36:P2038&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G35:G50 G53:G54 G57:G63 G65:G70 G72:G79 G81:G86 G88 G90 G95:G101 G106 G108 G380:G383">
-    <cfRule type="expression" dxfId="13" priority="54" stopIfTrue="1">
-      <formula>P36:P2037&gt;110000000</formula>
+  <conditionalFormatting sqref="G109">
+    <cfRule type="expression" dxfId="15" priority="68" stopIfTrue="1">
+      <formula>P110:P2113&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G109 G111:G115 G118:G143 G145:G155 G160:G162 G165 G167:G174 G177:G180 G183:G196 G199:G202 G204:G208 G210:G214 G216:G218 G220 G225:G233 G237:G239 G243:G246 G248:G249 G254:G258 G260:G261 G263:G268 G271 G273:G282 G286 G290:G299 G302:G306 G308 G310:G316 G318:G323 G325:G333 G336:G351 G353:G356 G359:G363 G365:G378">
-    <cfRule type="expression" dxfId="12" priority="64" stopIfTrue="1">
-      <formula>P110:P2112&gt;110000000</formula>
+  <conditionalFormatting sqref="G435 G386:G428 G430:G432 G437:G449 G451:G457 G459 G461:G463 G465:G472 G474:G476 G478 G481:G484 G486 G488 G493:G497 G499 G501:G503 G505:G506 G508:G509 G512:G518 G520 G522:G525 G527 G529:G530 G532:G533 G536:G539 G542 G544:G552 G555:G565 G567:G576 G579:G581">
+    <cfRule type="expression" dxfId="14" priority="76" stopIfTrue="1">
+      <formula>P387:P2388&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G386:G428 G430:G432 G435 G437:G449 G451:G457 G459 G461:G463 G465:G472 G474:G476 G478 G481:G484 G486 G488 G493:G497 G499 G501:G503 G505:G506 G508:G509 G512:G518 G520 G522:G525 G527 G529:G530 G532:G533 G536:G539 G542 G544:G552 G555:G565 G567:G576 G579:G581">
-    <cfRule type="expression" dxfId="11" priority="72" stopIfTrue="1">
-      <formula>P387:P2387&gt;110000000</formula>
+  <conditionalFormatting sqref="G665:G666 H667 G668:G673 H674:H675 G676:G678 H679:H680 G681:G697 H698:H699 G700:G705 H706:H707 G708:G717 H718 G719:G726 H727 G728:G737 H738 G739:G743 G745">
+    <cfRule type="expression" dxfId="13" priority="194" stopIfTrue="1">
+      <formula>#REF!&gt;110000000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G746:G748 G750 G753:G755 G757:G760 G762">
+    <cfRule type="expression" dxfId="12" priority="196" stopIfTrue="1">
+      <formula>I746:I2745&gt;110000000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15 H10:H12 H23:H26">
+    <cfRule type="expression" dxfId="11" priority="54" stopIfTrue="1">
+      <formula>P11:P2015&gt;110000000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H64 H51:H52 H55:H56 H71 H80 H87 H89 H91:H94 H102:H105 H384:H385">
+    <cfRule type="expression" dxfId="10" priority="62" stopIfTrue="1">
+      <formula>P52:P2054&gt;110000000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H110 H116:H117 H144 H158:H159 H163:H164 H166 H176 H181:H182 H197:H198 H203 H209 H215 H219 H221 H234:H236 H240:H242 H247 H253 H259 H262 H269:H270 H272 H307 H309 H317 H324 H334:H335 H352 H358 H364 H379">
+    <cfRule type="expression" dxfId="9" priority="72" stopIfTrue="1">
+      <formula>P111:P2114&gt;110000000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H429 H433:H434 H436 H450 H458 H460 H464 H473 H477 H479:H480 H487 H490:H492 H498 H500 H504 H507 H510:H511 H519 H521 H526 H528 H531 H535 H540:H541 H543 H553:H554 H566 H577:H578">
+    <cfRule type="expression" dxfId="8" priority="80" stopIfTrue="1">
+      <formula>P430:P2431&gt;110000000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H534">
+    <cfRule type="expression" dxfId="7" priority="45" stopIfTrue="1">
+      <formula>N541:N2542&gt;110000000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H586 H594 H606 H609:H610 H625:H626 H634 H642 H649 H655">
+    <cfRule type="expression" dxfId="6" priority="88" stopIfTrue="1">
+      <formula>P587:P2587&gt;110000000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H749 H751:H752 H756 H761">
+    <cfRule type="expression" dxfId="5" priority="198" stopIfTrue="1">
+      <formula>I749:I2748&gt;110000000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B761:B762">
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G9 G13:G14 G16:G22 G27:G34">
+    <cfRule type="expression" dxfId="3" priority="199" stopIfTrue="1">
+      <formula>P3:P2007&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G582:G585 G587:G593 G595:G602 G607:G608 G611:G624 G628:G633 G635:G641 G643:G648 G650:G654 G656:G662">
-    <cfRule type="expression" dxfId="10" priority="80" stopIfTrue="1">
-      <formula>P583:P2582&gt;110000000</formula>
+    <cfRule type="expression" dxfId="2" priority="276" stopIfTrue="1">
+      <formula>P583:P2583&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G665:G666 H667 G668:G673 H674:H675 G676:G678 H679:H680 G681:G697 H698:H699 G700:G705 H706:H707 G708:G717 H718 G719:G726 H727 G728:G737 H738 G739:G744">
-    <cfRule type="expression" dxfId="9" priority="190" stopIfTrue="1">
-      <formula>#REF!&gt;110000000</formula>
-    </cfRule>
+  <conditionalFormatting sqref="B744">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:H12 H15 H23:H26">
-    <cfRule type="expression" dxfId="8" priority="50" stopIfTrue="1">
-      <formula>P11:P2014&gt;110000000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H51:H52 H55:H56 H64 H71 H80 H87 H89 H91:H94 H102:H105 H384:H385">
-    <cfRule type="expression" dxfId="7" priority="58" stopIfTrue="1">
-      <formula>P52:P2053&gt;110000000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H110 H116:H117 H144 H158:H159 H163:H164 H166 H176 H181:H182 H197:H198 H203 H209 H215 H219 H221 H234:H236 H240:H242 H247 H253 H259 H262 H269:H270 H272 H307 H309 H317 H324 H334:H335 H352 H358 H364 H379">
-    <cfRule type="expression" dxfId="6" priority="68" stopIfTrue="1">
-      <formula>P111:P2113&gt;110000000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H429 H433:H434 H436 H450 H458 H460 H464 H473 H477 H479:H480 H487 H490:H492 H498 H500 H504 H507 H510:H511 H519 H521 H526 H528 H531 H535 H540:H541 H543 H553:H554 H566 H577:H578">
-    <cfRule type="expression" dxfId="5" priority="76" stopIfTrue="1">
-      <formula>P430:P2430&gt;110000000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H534">
-    <cfRule type="expression" dxfId="4" priority="41" stopIfTrue="1">
-      <formula>N541:N2541&gt;110000000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H586 H594 H606 H609:H610 H625:H626 H634 H642 H649 H655">
-    <cfRule type="expression" dxfId="3" priority="84" stopIfTrue="1">
-      <formula>P587:P2586&gt;110000000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B745:B759">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G756:G759 G752:G754 G749 G745:G747">
-    <cfRule type="expression" dxfId="1" priority="192" stopIfTrue="1">
-      <formula>I745:I2744&gt;110000000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H755 H750:H751 H748">
-    <cfRule type="expression" dxfId="0" priority="194" stopIfTrue="1">
-      <formula>I748:I2747&gt;110000000</formula>
+  <conditionalFormatting sqref="H744">
+    <cfRule type="expression" dxfId="0" priority="277" stopIfTrue="1">
+      <formula>I744:I2744&gt;110000000</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
